--- a/sdtm-test-codes/interim/Codelist_Cross_References.xlsx
+++ b/sdtm-test-codes/interim/Codelist_Cross_References.xlsx
@@ -484,7 +484,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Generated: 2026-09-30 18:19</t>
+          <t>Generated: 2026-10-01 10:39</t>
         </is>
       </c>
     </row>
